--- a/datasets/tenant-inputs/generated/meridian-health/standard-2026-07-v3/core-dimensions/11_risks_controls.xlsx
+++ b/datasets/tenant-inputs/generated/meridian-health/standard-2026-07-v3/core-dimensions/11_risks_controls.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start Here" sheetId="1" r:id="R8d994696b7384a9c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Client Intake" sheetId="2" r:id="Rf1247f61d7a347ea"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Questionnaire" sheetId="3" r:id="Rf545f8adc41e4d5d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Examples" sheetId="4" r:id="R708eecd6602e4cc3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference Values" sheetId="5" r:id="R0b58966d232d4423"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relationship Expectations" sheetId="6" r:id="Ra5440c961b0b4423"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start Here" sheetId="1" r:id="Rd68b3c26ed9b48d7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Client Intake" sheetId="2" r:id="Reb90c1b0c3204709"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Questionnaire" sheetId="3" r:id="Rd0af5d8a5d6e422e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Examples" sheetId="4" r:id="Ra8778ed7f827430d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference Values" sheetId="5" r:id="R3e583b22aac94cbb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relationship Expectations" sheetId="6" r:id="R7ec5ef249ab2449e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -624,7 +624,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra68363bc49a4484d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb08d6a88892945f8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -785,7 +785,7 @@
         <x:v>MERIDIAN-HEALTH-MH-ENTERPRISE-EV01</x:v>
       </x:c>
       <x:c r="M6" s="78" t="str">
-        <x:v>Need DQ rules, lineage export, owner sign-off, and remediation backlog.</x:v>
+        <x:v>Validate Executive Office data lineage and definition risk (record 1) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for risks controls.</x:v>
       </x:c>
       <x:c r="N6" s="41" t="str">
         <x:v>High</x:v>
@@ -829,7 +829,7 @@
         <x:v>MERIDIAN-HEALTH-MH-ENTERPRISE-EV02</x:v>
       </x:c>
       <x:c r="M7" s="79" t="str">
-        <x:v>Need actual incident history, root cause taxonomy, and change approval evidence.</x:v>
+        <x:v>Confirm Executive Office operational resilience and change risk (record 2) current-vs-target status, module boundary, volume baseline, and relationship links before this risks controls record is used downstream.</x:v>
       </x:c>
       <x:c r="N7" s="45" t="str">
         <x:v>Medium</x:v>
@@ -873,7 +873,7 @@
         <x:v>MERIDIAN-HEALTH-MH-CLINICAL-OPS-EV01</x:v>
       </x:c>
       <x:c r="M8" t="str">
-        <x:v>Need DQ rules, lineage export, owner sign-off, and remediation backlog.</x:v>
+        <x:v>Attach client evidence for Provider Operations data lineage and definition risk (record 3), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="N8" t="str">
         <x:v>High</x:v>
@@ -917,7 +917,7 @@
         <x:v>MERIDIAN-HEALTH-MH-CLINICAL-OPS-EV02</x:v>
       </x:c>
       <x:c r="M9" t="str">
-        <x:v>Need actual incident history, root cause taxonomy, and change approval evidence.</x:v>
+        <x:v>Reconcile Provider Operations operational resilience and change risk (record 4) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="N9" t="str">
         <x:v>Medium</x:v>
@@ -961,7 +961,7 @@
         <x:v>MERIDIAN-HEALTH-MH-CLAIMS-OPS-EV01</x:v>
       </x:c>
       <x:c r="M10" t="str">
-        <x:v>Need DQ rules, lineage export, owner sign-off, and remediation backlog.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Claims Operations data lineage and definition risk (record 5) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="N10" t="str">
         <x:v>High</x:v>
@@ -1005,7 +1005,7 @@
         <x:v>MERIDIAN-HEALTH-MH-CLAIMS-OPS-EV02</x:v>
       </x:c>
       <x:c r="M11" t="str">
-        <x:v>Need actual incident history, root cause taxonomy, and change approval evidence.</x:v>
+        <x:v>Validate Claims Operations operational resilience and change risk (record 6) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for risks controls.</x:v>
       </x:c>
       <x:c r="N11" t="str">
         <x:v>Medium</x:v>
@@ -1049,7 +1049,7 @@
         <x:v>MERIDIAN-HEALTH-MH-ELIGIBILITY-EV01</x:v>
       </x:c>
       <x:c r="M12" t="str">
-        <x:v>Need DQ rules, lineage export, owner sign-off, and remediation backlog.</x:v>
+        <x:v>Confirm Eligibility and Benefits data lineage and definition risk (record 7) current-vs-target status, module boundary, volume baseline, and relationship links before this risks controls record is used downstream.</x:v>
       </x:c>
       <x:c r="N12" t="str">
         <x:v>High</x:v>
@@ -1093,7 +1093,7 @@
         <x:v>MERIDIAN-HEALTH-MH-ELIGIBILITY-EV02</x:v>
       </x:c>
       <x:c r="M13" t="str">
-        <x:v>Need actual incident history, root cause taxonomy, and change approval evidence.</x:v>
+        <x:v>Attach client evidence for Eligibility and Benefits operational resilience and change risk (record 8), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="N13" t="str">
         <x:v>Medium</x:v>
@@ -1137,7 +1137,7 @@
         <x:v>MERIDIAN-HEALTH-MH-PRIOR-AUTH-EV01</x:v>
       </x:c>
       <x:c r="M14" t="str">
-        <x:v>Need DQ rules, lineage export, owner sign-off, and remediation backlog.</x:v>
+        <x:v>Reconcile Prior Authorization and UM data lineage and definition risk (record 9) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="N14" t="str">
         <x:v>High</x:v>
@@ -1181,7 +1181,7 @@
         <x:v>MERIDIAN-HEALTH-MH-PRIOR-AUTH-EV02</x:v>
       </x:c>
       <x:c r="M15" t="str">
-        <x:v>Need actual incident history, root cause taxonomy, and change approval evidence.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Prior Authorization and UM operational resilience and change risk (record 10) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="N15" t="str">
         <x:v>Medium</x:v>
@@ -1195,7 +1195,7 @@
         <x:v>Data quality / lineage / reporting</x:v>
       </x:c>
       <x:c r="C16" t="str">
-        <x:v>Definitions, lineage, and certification gaps could cause Contact Center and Member Service decisions to rely on inconsistent or stale context.</x:v>
+        <x:v>Agent Assist / Member Service risk: Agents search Salesforce cases, benefits notes, prior-auth status, and claims inquiry screens separately while the member waits on the call.</x:v>
       </x:c>
       <x:c r="D16" t="str">
         <x:v>Contact Center and Member Service</x:v>
@@ -1213,7 +1213,7 @@
         <x:v>Medium</x:v>
       </x:c>
       <x:c r="I16" t="str">
-        <x:v>Catalog source ownership, reconcile critical measures, certify data products, and expose gaps before module handoff.</x:v>
+        <x:v>Validate Genesys call sample with queue, intent, handle time, transfer flag, and after-call-work fields.; implement control around CRM-to-claims join gaps.</x:v>
       </x:c>
       <x:c r="J16" t="str">
         <x:v>Control design needed</x:v>
@@ -1225,7 +1225,7 @@
         <x:v>MERIDIAN-HEALTH-MH-CONTACT-CENTER-EV01</x:v>
       </x:c>
       <x:c r="M16" t="str">
-        <x:v>Need DQ rules, lineage export, owner sign-off, and remediation backlog.</x:v>
+        <x:v>Validate Contact Center and Member Service data lineage and definition risk (record 11) against Agent Assist / Member Service evidence: CRM-to-claims join gaps; confirm Genesys-Salesforce-claims context join owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="N16" t="str">
         <x:v>High</x:v>
@@ -1239,7 +1239,7 @@
         <x:v>Operational resilience / change control</x:v>
       </x:c>
       <x:c r="C17" t="str">
-        <x:v>Incidents, batch failures, interface breaks, or change collisions can degrade member calls, CRM case management, next-best-action workflows.</x:v>
+        <x:v>Agent Assist / Member Service risk: Call transcript intent labels are inconsistent across billing, eligibility, claims status, and prior authorization categories.</x:v>
       </x:c>
       <x:c r="D17" t="str">
         <x:v>Contact Center and Member Service</x:v>
@@ -1257,7 +1257,7 @@
         <x:v>Medium</x:v>
       </x:c>
       <x:c r="I17" t="str">
-        <x:v>Link incidents/problems/changes to systems, owners, SLAs, and Tower metrics.</x:v>
+        <x:v>Validate Salesforce Health Cloud case extract with member inquiry categories and resolution dispositions.; implement control around stale knowledge article duplicates.</x:v>
       </x:c>
       <x:c r="J17" t="str">
         <x:v>Partially evidenced from synthetic adapter rows</x:v>
@@ -1269,7 +1269,7 @@
         <x:v>MERIDIAN-HEALTH-MH-CONTACT-CENTER-EV02</x:v>
       </x:c>
       <x:c r="M17" t="str">
-        <x:v>Need actual incident history, root cause taxonomy, and change approval evidence.</x:v>
+        <x:v>Validate Contact Center and Member Service operational resilience and change risk (record 12) against Agent Assist / Member Service evidence: stale knowledge article duplicates; confirm human-approved next-best-action workflow owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="N17" t="str">
         <x:v>Medium</x:v>
@@ -1313,7 +1313,7 @@
         <x:v>MERIDIAN-HEALTH-MH-REVENUE-CYCLE-EV01</x:v>
       </x:c>
       <x:c r="M18" t="str">
-        <x:v>Need DQ rules, lineage export, owner sign-off, and remediation backlog.</x:v>
+        <x:v>Attach client evidence for Revenue Cycle Operations data lineage and definition risk (record 13), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="N18" t="str">
         <x:v>High</x:v>
@@ -1357,7 +1357,7 @@
         <x:v>MERIDIAN-HEALTH-MH-REVENUE-CYCLE-EV02</x:v>
       </x:c>
       <x:c r="M19" t="str">
-        <x:v>Need actual incident history, root cause taxonomy, and change approval evidence.</x:v>
+        <x:v>Reconcile Revenue Cycle Operations operational resilience and change risk (record 14) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="N19" t="str">
         <x:v>Medium</x:v>
@@ -1371,7 +1371,7 @@
         <x:v>Data quality / lineage / reporting</x:v>
       </x:c>
       <x:c r="C20" t="str">
-        <x:v>Definitions, lineage, and certification gaps could cause Finance Analytics decisions to rely on inconsistent or stale context.</x:v>
+        <x:v>Finance Analytics risk: Databricks Finance Gold is the target path, but cost-center hierarchy, vendor master harmonization, and audit signoff are unresolved.</x:v>
       </x:c>
       <x:c r="D20" t="str">
         <x:v>Finance Analytics</x:v>
@@ -1389,7 +1389,7 @@
         <x:v>Medium</x:v>
       </x:c>
       <x:c r="I20" t="str">
-        <x:v>Catalog source ownership, reconcile critical measures, certify data products, and expose gaps before module handoff.</x:v>
+        <x:v>Validate Finance Gold Data Product design notes for Databricks target certification.; implement control around incomplete lineage from ERP to BI.</x:v>
       </x:c>
       <x:c r="J20" t="str">
         <x:v>Control design needed</x:v>
@@ -1401,7 +1401,7 @@
         <x:v>MERIDIAN-HEALTH-MH-FINANCE-ANALYTICS-EV01</x:v>
       </x:c>
       <x:c r="M20" t="str">
-        <x:v>Need DQ rules, lineage export, owner sign-off, and remediation backlog.</x:v>
+        <x:v>Validate Finance Analytics data lineage and definition risk (record 15) against Finance Analytics evidence: incomplete lineage from ERP to BI; confirm cost-center hierarchy stewardship owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="N20" t="str">
         <x:v>High</x:v>
@@ -1415,7 +1415,7 @@
         <x:v>Operational resilience / change control</x:v>
       </x:c>
       <x:c r="C21" t="str">
-        <x:v>Incidents, batch failures, interface breaks, or change collisions can degrade GL/AP/AR/budget/vendor spend reporting, close analytics, FP&amp;A dashboards.</x:v>
+        <x:v>Finance Analytics risk: Month-end close dashboards slow down because 38 priority reports refresh from five SQL Server finance schemas during the same overnight load window.</x:v>
       </x:c>
       <x:c r="D21" t="str">
         <x:v>Finance Analytics</x:v>
@@ -1433,7 +1433,7 @@
         <x:v>Medium</x:v>
       </x:c>
       <x:c r="I21" t="str">
-        <x:v>Link incidents/problems/changes to systems, owners, SLAs, and Tower metrics.</x:v>
+        <x:v>Validate Oracle ERP Finance GL/AP/AR extract as of 2026-06 synthetic close cycle.; implement control around inconsistent vendor spend definitions.</x:v>
       </x:c>
       <x:c r="J21" t="str">
         <x:v>Partially evidenced from synthetic adapter rows</x:v>
@@ -1445,7 +1445,7 @@
         <x:v>MERIDIAN-HEALTH-MH-FINANCE-ANALYTICS-EV02</x:v>
       </x:c>
       <x:c r="M21" t="str">
-        <x:v>Need actual incident history, root cause taxonomy, and change approval evidence.</x:v>
+        <x:v>Validate Finance Analytics operational resilience and change risk (record 16) against Finance Analytics evidence: inconsistent vendor spend definitions; confirm Databricks Finance Gold certification owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="N21" t="str">
         <x:v>Medium</x:v>
@@ -1489,7 +1489,7 @@
         <x:v>MERIDIAN-HEALTH-MH-HR-WORKFORCE-EV01</x:v>
       </x:c>
       <x:c r="M22" t="str">
-        <x:v>Need DQ rules, lineage export, owner sign-off, and remediation backlog.</x:v>
+        <x:v>Confirm Workforce Analytics data lineage and definition risk (record 17) current-vs-target status, module boundary, volume baseline, and relationship links before this risks controls record is used downstream.</x:v>
       </x:c>
       <x:c r="N22" t="str">
         <x:v>High</x:v>
@@ -1533,7 +1533,7 @@
         <x:v>MERIDIAN-HEALTH-MH-HR-WORKFORCE-EV02</x:v>
       </x:c>
       <x:c r="M23" t="str">
-        <x:v>Need actual incident history, root cause taxonomy, and change approval evidence.</x:v>
+        <x:v>Attach client evidence for Workforce Analytics operational resilience and change risk (record 18), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="N23" t="str">
         <x:v>Medium</x:v>
@@ -1577,7 +1577,7 @@
         <x:v>MERIDIAN-HEALTH-MH-CLINICAL-QUALITY-EV01</x:v>
       </x:c>
       <x:c r="M24" t="str">
-        <x:v>Need DQ rules, lineage export, owner sign-off, and remediation backlog.</x:v>
+        <x:v>Reconcile Clinical Quality Analytics data lineage and definition risk (record 19) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="N24" t="str">
         <x:v>High</x:v>
@@ -1621,7 +1621,7 @@
         <x:v>MERIDIAN-HEALTH-MH-CLINICAL-QUALITY-EV02</x:v>
       </x:c>
       <x:c r="M25" t="str">
-        <x:v>Need actual incident history, root cause taxonomy, and change approval evidence.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Clinical Quality Analytics operational resilience and change risk (record 20) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="N25" t="str">
         <x:v>Medium</x:v>
@@ -1665,7 +1665,7 @@
         <x:v>MERIDIAN-HEALTH-MH-CLAIMS-ANALYTICS-EV01</x:v>
       </x:c>
       <x:c r="M26" t="str">
-        <x:v>Need DQ rules, lineage export, owner sign-off, and remediation backlog.</x:v>
+        <x:v>Validate Claims and Payment Analytics data lineage and definition risk (record 21) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for risks controls.</x:v>
       </x:c>
       <x:c r="N26" t="str">
         <x:v>High</x:v>
@@ -1709,7 +1709,7 @@
         <x:v>MERIDIAN-HEALTH-MH-CLAIMS-ANALYTICS-EV02</x:v>
       </x:c>
       <x:c r="M27" t="str">
-        <x:v>Need actual incident history, root cause taxonomy, and change approval evidence.</x:v>
+        <x:v>Confirm Claims and Payment Analytics operational resilience and change risk (record 22) current-vs-target status, module boundary, volume baseline, and relationship links before this risks controls record is used downstream.</x:v>
       </x:c>
       <x:c r="N27" t="str">
         <x:v>Medium</x:v>
@@ -1753,7 +1753,7 @@
         <x:v>MERIDIAN-HEALTH-MH-PROVIDER-PERFORMANCE-EV01</x:v>
       </x:c>
       <x:c r="M28" t="str">
-        <x:v>Need DQ rules, lineage export, owner sign-off, and remediation backlog.</x:v>
+        <x:v>Attach client evidence for Provider Performance Analytics data lineage and definition risk (record 23), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="N28" t="str">
         <x:v>High</x:v>
@@ -1797,7 +1797,7 @@
         <x:v>MERIDIAN-HEALTH-MH-PROVIDER-PERFORMANCE-EV02</x:v>
       </x:c>
       <x:c r="M29" t="str">
-        <x:v>Need actual incident history, root cause taxonomy, and change approval evidence.</x:v>
+        <x:v>Reconcile Provider Performance Analytics operational resilience and change risk (record 24) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="N29" t="str">
         <x:v>Medium</x:v>
@@ -1841,7 +1841,7 @@
         <x:v>MERIDIAN-HEALTH-MH-DATA-PLATFORM-EV01</x:v>
       </x:c>
       <x:c r="M30" t="str">
-        <x:v>Need DQ rules, lineage export, owner sign-off, and remediation backlog.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Enterprise Data Platform data lineage and definition risk (record 25) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="N30" t="str">
         <x:v>High</x:v>
@@ -1885,7 +1885,7 @@
         <x:v>MERIDIAN-HEALTH-MH-DATA-PLATFORM-EV02</x:v>
       </x:c>
       <x:c r="M31" t="str">
-        <x:v>Need actual incident history, root cause taxonomy, and change approval evidence.</x:v>
+        <x:v>Validate Enterprise Data Platform operational resilience and change risk (record 26) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for risks controls.</x:v>
       </x:c>
       <x:c r="N31" t="str">
         <x:v>Medium</x:v>
@@ -1929,7 +1929,7 @@
         <x:v>MERIDIAN-HEALTH-MH-DATA-GOVERNANCE-EV01</x:v>
       </x:c>
       <x:c r="M32" t="str">
-        <x:v>Need DQ rules, lineage export, owner sign-off, and remediation backlog.</x:v>
+        <x:v>Confirm Data Governance and Data Quality data lineage and definition risk (record 27) current-vs-target status, module boundary, volume baseline, and relationship links before this risks controls record is used downstream.</x:v>
       </x:c>
       <x:c r="N32" t="str">
         <x:v>High</x:v>
@@ -1973,7 +1973,7 @@
         <x:v>MERIDIAN-HEALTH-MH-DATA-GOVERNANCE-EV02</x:v>
       </x:c>
       <x:c r="M33" t="str">
-        <x:v>Need actual incident history, root cause taxonomy, and change approval evidence.</x:v>
+        <x:v>Attach client evidence for Data Governance and Data Quality operational resilience and change risk (record 28), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="N33" t="str">
         <x:v>Medium</x:v>
@@ -1987,7 +1987,7 @@
         <x:v>Data quality / lineage / reporting</x:v>
       </x:c>
       <x:c r="C34" t="str">
-        <x:v>Definitions, lineage, and certification gaps could cause Agent Assist and Next Best Action decisions to rely on inconsistent or stale context.</x:v>
+        <x:v>Agent Assist / Member Service risk: Knowledge articles are duplicated across operations playbooks and CRM snippets, creating conflicting guidance for appeal and denial inquiries.</x:v>
       </x:c>
       <x:c r="D34" t="str">
         <x:v>Agent Assist and Next Best Action</x:v>
@@ -2005,7 +2005,7 @@
         <x:v>Medium</x:v>
       </x:c>
       <x:c r="I34" t="str">
-        <x:v>Catalog source ownership, reconcile critical measures, certify data products, and expose gaps before module handoff.</x:v>
+        <x:v>Validate Knowledge article export with duplicate and stale article flags.; implement control around CRM-to-claims join gaps.</x:v>
       </x:c>
       <x:c r="J34" t="str">
         <x:v>Control design needed</x:v>
@@ -2017,7 +2017,7 @@
         <x:v>MERIDIAN-HEALTH-MH-AGENT-ASSIST-EV01</x:v>
       </x:c>
       <x:c r="M34" t="str">
-        <x:v>Need DQ rules, lineage export, owner sign-off, and remediation backlog.</x:v>
+        <x:v>Validate Agent Assist and Next Best Action data lineage and definition risk (record 29) against Agent Assist / Member Service evidence: CRM-to-claims join gaps; confirm Genesys-Salesforce-claims context join owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="N34" t="str">
         <x:v>High</x:v>
@@ -2031,7 +2031,7 @@
         <x:v>Operational resilience / change control</x:v>
       </x:c>
       <x:c r="C35" t="str">
-        <x:v>Incidents, batch failures, interface breaks, or change collisions can degrade agent assist, call summarization, intent detection, guided resolution.</x:v>
+        <x:v>Agent Assist / Member Service risk: Supervisors cannot prove whether AI suggestions reduce handle time without a baseline for after-call work, transfer rate, and first-contact resolution.</x:v>
       </x:c>
       <x:c r="D35" t="str">
         <x:v>Agent Assist and Next Best Action</x:v>
@@ -2049,7 +2049,7 @@
         <x:v>Medium</x:v>
       </x:c>
       <x:c r="I35" t="str">
-        <x:v>Link incidents/problems/changes to systems, owners, SLAs, and Tower metrics.</x:v>
+        <x:v>Validate Member service KPI baseline for AHT, FCR, transfer rate, complaint escalation, and quality score.; implement control around stale knowledge article duplicates.</x:v>
       </x:c>
       <x:c r="J35" t="str">
         <x:v>Partially evidenced from synthetic adapter rows</x:v>
@@ -2061,7 +2061,7 @@
         <x:v>MERIDIAN-HEALTH-MH-AGENT-ASSIST-EV02</x:v>
       </x:c>
       <x:c r="M35" t="str">
-        <x:v>Need actual incident history, root cause taxonomy, and change approval evidence.</x:v>
+        <x:v>Validate Agent Assist and Next Best Action operational resilience and change risk (record 30) against Agent Assist / Member Service evidence: stale knowledge article duplicates; confirm human-approved next-best-action workflow owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="N35" t="str">
         <x:v>Medium</x:v>
@@ -2105,7 +2105,7 @@
         <x:v>MERIDIAN-HEALTH-MH-UNIFIED-LAKEHOUSE-EV01</x:v>
       </x:c>
       <x:c r="M36" t="str">
-        <x:v>Need DQ rules, lineage export, owner sign-off, and remediation backlog.</x:v>
+        <x:v>Validate Unified Clinical and Claims Lakehouse data lineage and definition risk (record 31) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for risks controls.</x:v>
       </x:c>
       <x:c r="N36" t="str">
         <x:v>High</x:v>
@@ -2149,7 +2149,7 @@
         <x:v>MERIDIAN-HEALTH-MH-UNIFIED-LAKEHOUSE-EV02</x:v>
       </x:c>
       <x:c r="M37" t="str">
-        <x:v>Need actual incident history, root cause taxonomy, and change approval evidence.</x:v>
+        <x:v>Confirm Unified Clinical and Claims Lakehouse operational resilience and change risk (record 32) current-vs-target status, module boundary, volume baseline, and relationship links before this risks controls record is used downstream.</x:v>
       </x:c>
       <x:c r="N37" t="str">
         <x:v>Medium</x:v>
@@ -2193,7 +2193,7 @@
         <x:v>MERIDIAN-HEALTH-MH-IT-BUDGET-EV01</x:v>
       </x:c>
       <x:c r="M38" t="str">
-        <x:v>Need DQ rules, lineage export, owner sign-off, and remediation backlog.</x:v>
+        <x:v>Attach client evidence for IT Budget and Tower Baseline data lineage and definition risk (record 33), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="N38" t="str">
         <x:v>High</x:v>
@@ -2237,7 +2237,7 @@
         <x:v>MERIDIAN-HEALTH-MH-IT-BUDGET-EV02</x:v>
       </x:c>
       <x:c r="M39" t="str">
-        <x:v>Need actual incident history, root cause taxonomy, and change approval evidence.</x:v>
+        <x:v>Reconcile IT Budget and Tower Baseline operational resilience and change risk (record 34) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="N39" t="str">
         <x:v>Medium</x:v>
@@ -2281,7 +2281,7 @@
         <x:v>MERIDIAN-HEALTH-MH-VENDOR-SOURCING-EV01</x:v>
       </x:c>
       <x:c r="M40" t="str">
-        <x:v>Need DQ rules, lineage export, owner sign-off, and remediation backlog.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Vendor and Contract Optimization data lineage and definition risk (record 35) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="N40" t="str">
         <x:v>High</x:v>
@@ -2325,7 +2325,7 @@
         <x:v>MERIDIAN-HEALTH-MH-VENDOR-SOURCING-EV02</x:v>
       </x:c>
       <x:c r="M41" t="str">
-        <x:v>Need actual incident history, root cause taxonomy, and change approval evidence.</x:v>
+        <x:v>Validate Vendor and Contract Optimization operational resilience and change risk (record 36) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for risks controls.</x:v>
       </x:c>
       <x:c r="N41" t="str">
         <x:v>Medium</x:v>
@@ -2369,7 +2369,7 @@
         <x:v>MERIDIAN-HEALTH-MH-CMDB-INFRA-EV01</x:v>
       </x:c>
       <x:c r="M42" t="str">
-        <x:v>Need DQ rules, lineage export, owner sign-off, and remediation backlog.</x:v>
+        <x:v>Confirm Infrastructure and CMDB data lineage and definition risk (record 37) current-vs-target status, module boundary, volume baseline, and relationship links before this risks controls record is used downstream.</x:v>
       </x:c>
       <x:c r="N42" t="str">
         <x:v>High</x:v>
@@ -2413,7 +2413,7 @@
         <x:v>MERIDIAN-HEALTH-MH-CMDB-INFRA-EV02</x:v>
       </x:c>
       <x:c r="M43" t="str">
-        <x:v>Need actual incident history, root cause taxonomy, and change approval evidence.</x:v>
+        <x:v>Attach client evidence for Infrastructure and CMDB operational resilience and change risk (record 38), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="N43" t="str">
         <x:v>Medium</x:v>
@@ -2457,7 +2457,7 @@
         <x:v>MERIDIAN-HEALTH-MH-INCIDENTS-EV01</x:v>
       </x:c>
       <x:c r="M44" t="str">
-        <x:v>Need DQ rules, lineage export, owner sign-off, and remediation backlog.</x:v>
+        <x:v>Reconcile Incident Problem Change Operations data lineage and definition risk (record 39) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="N44" t="str">
         <x:v>High</x:v>
@@ -2501,7 +2501,7 @@
         <x:v>MERIDIAN-HEALTH-MH-INCIDENTS-EV02</x:v>
       </x:c>
       <x:c r="M45" t="str">
-        <x:v>Need actual incident history, root cause taxonomy, and change approval evidence.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Incident Problem Change Operations operational resilience and change risk (record 40) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="N45" t="str">
         <x:v>Medium</x:v>
@@ -2528,7 +2528,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd6c96311369d4ce1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re77fafd1ef264a75"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2603,7 +2603,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R37208f81bd0147ad"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0ff18d76b0b5405d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2777,7 +2777,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2d153ae855894355"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5d57ff40fd1c4bab"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2855,7 +2855,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R40759a40503f485d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra4a10e45146f4adf"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2965,7 +2965,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfb0dcd724a524512"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R27ccd7e3095941df"/>
   </x:tableParts>
 </x:worksheet>
 </file>